--- a/runrun_report/Escopo Nuclea.xlsx
+++ b/runrun_report/Escopo Nuclea.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.esposito\vs_code_files\bia\runrun\runrun_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caio\Documents\GitHub\bia-runrunit\runrun_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9DDD724-4E77-4E33-82DF-A9FCCD4CA868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{82E0EDEA-BD92-42CB-8408-85F5220000AD}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="PROD" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
   <si>
     <t>PROJETO</t>
   </si>
@@ -280,13 +279,16 @@
   </si>
   <si>
     <t>GRUPOS</t>
+  </si>
+  <si>
+    <t>cooldown_dias</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,6 +319,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -729,7 +737,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -890,6 +898,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1223,17 +1232,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D5485E6-4F95-4942-8B98-A1F4334A065D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E31"/>
-  <sheetFormatPr defaultColWidth="52" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="52" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:5" ht="15" thickBot="1"/>
+    <row r="2" spans="2:5" ht="23.25" thickBot="1">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1247,7 +1256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" ht="23.25" thickBot="1">
       <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" ht="15" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
@@ -1275,7 +1284,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" ht="23.25" thickBot="1">
       <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
@@ -1289,7 +1298,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" ht="34.5" thickBot="1">
       <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
@@ -1301,7 +1310,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" ht="15" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>10</v>
       </c>
@@ -1315,7 +1324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" ht="15" thickBot="1">
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
@@ -1329,7 +1338,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" ht="15" thickBot="1">
       <c r="B9" s="12" t="s">
         <v>13</v>
       </c>
@@ -1343,7 +1352,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" ht="15" thickBot="1">
       <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
@@ -1357,7 +1366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" ht="15" thickBot="1">
       <c r="B11" s="12" t="s">
         <v>13</v>
       </c>
@@ -1369,7 +1378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" ht="15" thickBot="1">
       <c r="B12" s="16" t="s">
         <v>17</v>
       </c>
@@ -1383,7 +1392,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" ht="23.25" thickBot="1">
       <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
@@ -1395,7 +1404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" ht="23.25" thickBot="1">
       <c r="B14" s="8" t="s">
         <v>19</v>
       </c>
@@ -1407,7 +1416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" ht="23.25" thickBot="1">
       <c r="B15" s="12" t="s">
         <v>19</v>
       </c>
@@ -1419,7 +1428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" ht="23.25" thickBot="1">
       <c r="B16" s="8" t="s">
         <v>19</v>
       </c>
@@ -1431,7 +1440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" ht="23.25" thickBot="1">
       <c r="B17" s="12" t="s">
         <v>19</v>
       </c>
@@ -1445,7 +1454,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" ht="23.25" thickBot="1">
       <c r="B18" s="8" t="s">
         <v>19</v>
       </c>
@@ -1459,7 +1468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" ht="23.25" thickBot="1">
       <c r="B19" s="12" t="s">
         <v>19</v>
       </c>
@@ -1473,7 +1482,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" ht="23.25" thickBot="1">
       <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
@@ -1487,7 +1496,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" ht="23.25" thickBot="1">
       <c r="B21" s="19" t="s">
         <v>19</v>
       </c>
@@ -1499,7 +1508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" ht="15" thickBot="1">
       <c r="B22" s="4" t="s">
         <v>29</v>
       </c>
@@ -1513,7 +1522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" ht="15" thickBot="1">
       <c r="B23" s="12" t="s">
         <v>29</v>
       </c>
@@ -1527,7 +1536,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" ht="23.25" thickBot="1">
       <c r="B24" s="8" t="s">
         <v>29</v>
       </c>
@@ -1541,7 +1550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" ht="23.25" thickBot="1">
       <c r="B25" s="12" t="s">
         <v>29</v>
       </c>
@@ -1555,7 +1564,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" ht="23.25" thickBot="1">
       <c r="B26" s="8" t="s">
         <v>29</v>
       </c>
@@ -1569,7 +1578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" ht="23.25" thickBot="1">
       <c r="B27" s="12" t="s">
         <v>29</v>
       </c>
@@ -1583,7 +1592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" ht="23.25" thickBot="1">
       <c r="B28" s="8" t="s">
         <v>36</v>
       </c>
@@ -1595,7 +1604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" ht="23.25" thickBot="1">
       <c r="B29" s="12" t="s">
         <v>36</v>
       </c>
@@ -1607,7 +1616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:5" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" ht="23.25" thickBot="1">
       <c r="B30" s="8" t="s">
         <v>36</v>
       </c>
@@ -1619,7 +1628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="2:5" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" ht="22.5">
       <c r="B31" s="19" t="s">
         <v>36</v>
       </c>
@@ -1637,16 +1646,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F44E9D4-12E4-4E4C-872C-414D1EF8A6E0}">
-  <dimension ref="B2:E31"/>
-  <sheetFormatPr defaultColWidth="52" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:F31"/>
+  <sheetFormatPr defaultColWidth="52" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.21875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.25" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="16.5" thickBot="1">
       <c r="B2" s="30" t="s">
         <v>79</v>
       </c>
@@ -1659,8 +1668,11 @@
       <c r="E2" s="30" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="54" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
       <c r="B3" s="31" t="s">
         <v>75</v>
       </c>
@@ -1673,8 +1685,11 @@
       <c r="E3" s="34">
         <v>240</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
       <c r="B4" s="35" t="s">
         <v>75</v>
       </c>
@@ -1687,8 +1702,11 @@
       <c r="E4" s="36">
         <v>144</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="15" thickBot="1">
       <c r="B5" s="37" t="s">
         <v>75</v>
       </c>
@@ -1701,8 +1719,11 @@
       <c r="E5" s="40">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="15" thickBot="1">
       <c r="B6" s="41" t="s">
         <v>76</v>
       </c>
@@ -1713,8 +1734,11 @@
       <c r="E6" s="44">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="31" t="s">
         <v>78</v>
       </c>
@@ -1727,8 +1751,11 @@
       <c r="E7" s="34">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="15" thickBot="1">
       <c r="B8" s="45" t="s">
         <v>78</v>
       </c>
@@ -1741,8 +1768,11 @@
       <c r="E8" s="48">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
       <c r="B9" s="31" t="s">
         <v>77</v>
       </c>
@@ -1755,8 +1785,11 @@
       <c r="E9" s="34">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
       <c r="B10" s="35" t="s">
         <v>77</v>
       </c>
@@ -1769,8 +1802,11 @@
       <c r="E10" s="36">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="15" thickBot="1">
       <c r="B11" s="37" t="s">
         <v>77</v>
       </c>
@@ -1781,8 +1817,11 @@
       <c r="E11" s="40">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="15" thickBot="1">
       <c r="B12" s="41" t="s">
         <v>74</v>
       </c>
@@ -1795,8 +1834,11 @@
       <c r="E12" s="44">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
       <c r="B13" s="31" t="s">
         <v>70</v>
       </c>
@@ -1807,8 +1849,11 @@
       <c r="E13" s="34">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
       <c r="B14" s="35" t="s">
         <v>70</v>
       </c>
@@ -1819,8 +1864,11 @@
       <c r="E14" s="36">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
       <c r="B15" s="52" t="s">
         <v>70</v>
       </c>
@@ -1831,8 +1879,11 @@
       <c r="E15" s="53">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
       <c r="B16" s="35" t="s">
         <v>70</v>
       </c>
@@ -1843,8 +1894,11 @@
       <c r="E16" s="36">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
       <c r="B17" s="52" t="s">
         <v>70</v>
       </c>
@@ -1857,8 +1911,11 @@
       <c r="E17" s="53">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="35" t="s">
         <v>70</v>
       </c>
@@ -1871,8 +1928,11 @@
       <c r="E18" s="36">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
       <c r="B19" s="52" t="s">
         <v>70</v>
       </c>
@@ -1885,8 +1945,11 @@
       <c r="E19" s="53">
         <v>12</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="35" t="s">
         <v>70</v>
       </c>
@@ -1899,8 +1962,11 @@
       <c r="E20" s="36">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="15" thickBot="1">
       <c r="B21" s="37" t="s">
         <v>70</v>
       </c>
@@ -1911,8 +1977,11 @@
       <c r="E21" s="40">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
       <c r="B22" s="31" t="s">
         <v>69</v>
       </c>
@@ -1925,8 +1994,11 @@
       <c r="E22" s="34">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
       <c r="B23" s="52" t="s">
         <v>69</v>
       </c>
@@ -1939,8 +2011,11 @@
       <c r="E23" s="53">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
       <c r="B24" s="35" t="s">
         <v>69</v>
       </c>
@@ -1953,8 +2028,11 @@
       <c r="E24" s="36">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
       <c r="B25" s="52" t="s">
         <v>69</v>
       </c>
@@ -1967,8 +2045,11 @@
       <c r="E25" s="53">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
       <c r="B26" s="35" t="s">
         <v>69</v>
       </c>
@@ -1981,8 +2062,11 @@
       <c r="E26" s="36">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="B27" s="52" t="s">
         <v>69</v>
       </c>
@@ -1995,8 +2079,11 @@
       <c r="E27" s="53">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
       <c r="B28" s="35" t="s">
         <v>69</v>
       </c>
@@ -2007,8 +2094,11 @@
       <c r="E28" s="36">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
       <c r="B29" s="52" t="s">
         <v>69</v>
       </c>
@@ -2019,8 +2109,11 @@
       <c r="E29" s="53">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="35" t="s">
         <v>69</v>
       </c>
@@ -2031,8 +2124,11 @@
       <c r="E30" s="36">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F30">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="15" thickBot="1">
       <c r="B31" s="37" t="s">
         <v>69</v>
       </c>
@@ -2043,8 +2139,12 @@
       <c r="E31" s="40">
         <v>6</v>
       </c>
+      <c r="F31">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/runrun_report/Escopo Nuclea.xlsx
+++ b/runrun_report/Escopo Nuclea.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caio\Documents\GitHub\bia-runrunit\runrun_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caiofs\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9583B48B-997D-4953-B233-DE9ABB930893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="2250" yWindow="2310" windowWidth="18900" windowHeight="10965" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="PROD" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
   <si>
     <t>PROJETO</t>
   </si>
@@ -179,12 +177,6 @@
     <t>Landing pages</t>
   </si>
   <si>
-    <t>Artigos para o blog</t>
-  </si>
-  <si>
-    <t>Fluxos automatizados emkt</t>
-  </si>
-  <si>
     <t>Emkt único</t>
   </si>
   <si>
@@ -230,9 +222,6 @@
     <t>Peças para TV campanhas internas</t>
   </si>
   <si>
-    <t>Peças para Yammer campanhas internas</t>
-  </si>
-  <si>
     <t>Banners intranet campanhas internas</t>
   </si>
   <si>
@@ -242,18 +231,6 @@
     <t>Peças para TV campanha marca empregadora</t>
   </si>
   <si>
-    <t>Peças para Yammer campanha marca empregadora</t>
-  </si>
-  <si>
-    <t>Banners intranet campanha marca empregadora</t>
-  </si>
-  <si>
-    <t>02_Comunicação Intena (CI)</t>
-  </si>
-  <si>
-    <t>03_Eventos</t>
-  </si>
-  <si>
     <t>ENTREGÁVEIS</t>
   </si>
   <si>
@@ -263,32 +240,50 @@
     <t>QUANTIDADE/ANO</t>
   </si>
   <si>
-    <t>Geral</t>
-  </si>
-  <si>
-    <t>04_Redes Sociais (Social)</t>
-  </si>
-  <si>
-    <t>06_Mídia Paga</t>
-  </si>
-  <si>
-    <t>07_CRM</t>
-  </si>
-  <si>
-    <t>08_Conteúdo Rico (CR)</t>
-  </si>
-  <si>
     <t>GRUPOS</t>
   </si>
   <si>
     <t>cooldown_dias</t>
+  </si>
+  <si>
+    <t>Redes Sociais (Social)</t>
+  </si>
+  <si>
+    <t>Mídia Paga</t>
+  </si>
+  <si>
+    <t>Landing Page</t>
+  </si>
+  <si>
+    <t>Apresentação</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Conteúdo e layout de página para site</t>
+  </si>
+  <si>
+    <t>Eventos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eventos Patrocinados: KV </t>
+  </si>
+  <si>
+    <t>KV - Contempla conteúdo e layout</t>
+  </si>
+  <si>
+    <t>Peças gráficas de mobilização</t>
+  </si>
+  <si>
+    <t>Peças gráficas de eventos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,8 +320,30 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,8 +368,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -568,176 +603,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -808,100 +680,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{958466DC-D0E2-4E40-BBAF-A512253F5F8E}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{BC619484-4B65-409D-BCB4-BBB7E84D0446}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1232,16 +1037,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E31"/>
-  <sheetFormatPr defaultColWidth="52" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="52" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15" thickBot="1"/>
+    <row r="1" spans="2:5" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:5" ht="23.25" thickBot="1">
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1270,7 +1075,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="15" thickBot="1">
+    <row r="4" spans="2:5" ht="15.75" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
@@ -1310,7 +1115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="15" thickBot="1">
+    <row r="7" spans="2:5" ht="15.75" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>10</v>
       </c>
@@ -1324,7 +1129,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15" thickBot="1">
+    <row r="8" spans="2:5" ht="15.75" thickBot="1">
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
@@ -1338,7 +1143,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="15" thickBot="1">
+    <row r="9" spans="2:5" ht="15.75" thickBot="1">
       <c r="B9" s="12" t="s">
         <v>13</v>
       </c>
@@ -1352,7 +1157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="15" thickBot="1">
+    <row r="10" spans="2:5" ht="15.75" thickBot="1">
       <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
@@ -1366,7 +1171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="15" thickBot="1">
+    <row r="11" spans="2:5" ht="15.75" thickBot="1">
       <c r="B11" s="12" t="s">
         <v>13</v>
       </c>
@@ -1378,7 +1183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="15" thickBot="1">
+    <row r="12" spans="2:5" ht="15.75" thickBot="1">
       <c r="B12" s="16" t="s">
         <v>17</v>
       </c>
@@ -1508,7 +1313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="15" thickBot="1">
+    <row r="22" spans="2:5" ht="15.75" thickBot="1">
       <c r="B22" s="4" t="s">
         <v>29</v>
       </c>
@@ -1522,7 +1327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="15" thickBot="1">
+    <row r="23" spans="2:5" ht="15.75" thickBot="1">
       <c r="B23" s="12" t="s">
         <v>29</v>
       </c>
@@ -1646,43 +1451,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:F31"/>
-  <sheetFormatPr defaultColWidth="52" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="52" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.28515625" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="16.5" thickBot="1">
-      <c r="B2" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="54" t="s">
-        <v>80</v>
+    <row r="2" spans="2:6">
+      <c r="B2" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="32" t="s">
+      <c r="B3" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="27">
+        <f>E3/12</f>
         <v>20</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="27">
         <v>240</v>
       </c>
       <c r="F3">
@@ -1690,99 +1496,104 @@
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="35" t="s">
-        <v>75</v>
+      <c r="B4" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>42</v>
       </c>
       <c r="D4" s="27">
-        <v>12</v>
-      </c>
-      <c r="E4" s="36">
+        <f t="shared" ref="D4:D31" si="0">E4/12</f>
+        <v>12</v>
+      </c>
+      <c r="E4" s="27">
         <v>144</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15" thickBot="1">
-      <c r="B5" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="38" t="s">
+    <row r="5" spans="2:6">
+      <c r="B5" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="27">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="27">
         <v>48</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15" thickBot="1">
-      <c r="B6" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="42" t="s">
+    <row r="6" spans="2:6">
+      <c r="B6" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="44">
-        <v>50</v>
+      <c r="D6" s="27">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E6" s="27">
+        <v>60</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="32" t="s">
+      <c r="B7" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="33">
-        <v>2</v>
-      </c>
-      <c r="E7" s="34">
-        <v>24</v>
+      <c r="D7" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E7" s="27">
+        <v>12</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="15" thickBot="1">
-      <c r="B8" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="47">
-        <v>4</v>
-      </c>
-      <c r="E8" s="48">
-        <v>48</v>
+    <row r="8" spans="2:6">
+      <c r="B8" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27">
+        <v>1</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="33">
-        <v>1</v>
-      </c>
-      <c r="E9" s="34">
+      <c r="B9" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E9" s="27">
         <v>12</v>
       </c>
       <c r="F9">
@@ -1790,63 +1601,62 @@
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="35" t="s">
-        <v>77</v>
+      <c r="B10" s="26" t="s">
+        <v>72</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="27">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="27">
         <v>24</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="15" thickBot="1">
-      <c r="B11" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="40">
-        <v>2</v>
+    <row r="11" spans="2:6">
+      <c r="B11" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="29">
+        <v>6</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="15" thickBot="1">
-      <c r="B12" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="50">
-        <v>2</v>
-      </c>
-      <c r="E12" s="44">
-        <v>24</v>
+    <row r="12" spans="2:6">
+      <c r="B12" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27">
+        <v>5</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="34">
+      <c r="B13" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27">
         <v>5</v>
       </c>
       <c r="F13">
@@ -1854,14 +1664,14 @@
       </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="35" t="s">
-        <v>70</v>
+      <c r="B14" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="36">
+        <v>49</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27">
         <v>5</v>
       </c>
       <c r="F14">
@@ -1869,29 +1679,29 @@
       </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="53">
-        <v>5</v>
+      <c r="B15" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="29">
+        <v>10</v>
       </c>
       <c r="F15">
         <v>150</v>
       </c>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="36">
+      <c r="B16" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27">
         <v>5</v>
       </c>
       <c r="F16">
@@ -1899,33 +1709,32 @@
       </c>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="25">
-        <v>1</v>
-      </c>
-      <c r="E17" s="53">
-        <v>12</v>
+      <c r="B17" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27">
+        <v>4</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="35" t="s">
-        <v>70</v>
+      <c r="B18" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D18" s="27">
-        <v>1</v>
-      </c>
-      <c r="E18" s="36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E18" s="27">
         <v>12</v>
       </c>
       <c r="F18">
@@ -1933,16 +1742,17 @@
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="25">
-        <v>1</v>
-      </c>
-      <c r="E19" s="53">
+      <c r="B19" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E19" s="27">
         <v>12</v>
       </c>
       <c r="F19">
@@ -1950,116 +1760,119 @@
       </c>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="35" t="s">
-        <v>70</v>
+      <c r="B20" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D20" s="27">
-        <v>1</v>
-      </c>
-      <c r="E20" s="36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E20" s="27">
         <v>12</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="15" thickBot="1">
-      <c r="B21" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="40">
-        <v>1</v>
+    <row r="21" spans="2:6">
+      <c r="B21" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E21" s="27">
+        <v>12</v>
       </c>
       <c r="F21">
         <v>200</v>
       </c>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="33">
-        <v>1</v>
-      </c>
-      <c r="E22" s="34">
-        <v>12</v>
+      <c r="B22" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27">
+        <v>1</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="25">
-        <v>4</v>
-      </c>
-      <c r="E23" s="53">
-        <v>48</v>
+      <c r="B23" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E23" s="31">
+        <v>12</v>
       </c>
       <c r="F23">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>61</v>
+      <c r="B24" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>58</v>
       </c>
       <c r="D24" s="27">
-        <v>1</v>
-      </c>
-      <c r="E24" s="36">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E24" s="31">
+        <v>48</v>
       </c>
       <c r="F24">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="25">
-        <v>1</v>
-      </c>
-      <c r="E25" s="53">
-        <v>12</v>
+      <c r="B25" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="31">
+        <v>1</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>63</v>
+      <c r="B26" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>59</v>
       </c>
       <c r="D26" s="27">
-        <v>1</v>
-      </c>
-      <c r="E26" s="36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E26" s="31">
         <v>12</v>
       </c>
       <c r="F26">
@@ -2067,16 +1880,17 @@
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="25">
-        <v>1</v>
-      </c>
-      <c r="E27" s="53">
+      <c r="B27" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E27" s="31">
         <v>12</v>
       </c>
       <c r="F27">
@@ -2084,59 +1898,65 @@
       </c>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="36">
-        <v>6</v>
+      <c r="B28" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E28" s="31">
+        <v>12</v>
       </c>
       <c r="F28">
         <v>90</v>
       </c>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="53">
-        <v>6</v>
+      <c r="B29" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="31">
+        <v>12</v>
       </c>
       <c r="F29">
         <v>90</v>
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="28"/>
-      <c r="E30" s="36">
+      <c r="B30" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="34">
         <v>6</v>
       </c>
       <c r="F30">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="15" thickBot="1">
-      <c r="B31" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="49"/>
-      <c r="E31" s="40">
+    <row r="31" spans="2:6">
+      <c r="B31" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="27"/>
+      <c r="E31" s="34">
         <v>6</v>
       </c>
       <c r="F31">

--- a/runrun_report/Escopo Nuclea.xlsx
+++ b/runrun_report/Escopo Nuclea.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caiofs\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9583B48B-997D-4953-B233-DE9ABB930893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7ED2E4-3A2D-4852-8184-947E65D9CB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2310" windowWidth="18900" windowHeight="10965" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9300" yWindow="3000" windowWidth="12540" windowHeight="10965" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
   <si>
     <t>PROJETO</t>
   </si>
@@ -192,9 +192,6 @@
     <t>E-mails de convite eventos patrocinados</t>
   </si>
   <si>
-    <t>Layouts para stand eventos patrocinados</t>
-  </si>
-  <si>
     <t>E-mails de convite Núclea Day</t>
   </si>
   <si>
@@ -261,29 +258,29 @@
     <t>Site</t>
   </si>
   <si>
-    <t>Conteúdo e layout de página para site</t>
-  </si>
-  <si>
     <t>Eventos</t>
   </si>
   <si>
-    <t xml:space="preserve">Eventos Patrocinados: KV </t>
-  </si>
-  <si>
-    <t>KV - Contempla conteúdo e layout</t>
-  </si>
-  <si>
     <t>Peças gráficas de mobilização</t>
   </si>
   <si>
     <t>Peças gráficas de eventos</t>
+  </si>
+  <si>
+    <t>Layout para stand</t>
+  </si>
+  <si>
+    <t>KV de eventos</t>
+  </si>
+  <si>
+    <t>KV de mobilização</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,14 +325,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -701,7 +690,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1462,24 +1451,24 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="B2" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>67</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="26" t="s">
         <v>41</v>
@@ -1497,13 +1486,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>42</v>
       </c>
       <c r="D4" s="27">
-        <f t="shared" ref="D4:D31" si="0">E4/12</f>
+        <f t="shared" ref="D4:D29" si="0">E4/12</f>
         <v>12</v>
       </c>
       <c r="E4" s="27">
@@ -1515,7 +1504,7 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="26" t="s">
         <v>43</v>
@@ -1533,7 +1522,7 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>44</v>
@@ -1551,7 +1540,7 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>45</v>
@@ -1602,7 +1591,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="B10" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>47</v>
@@ -1620,10 +1609,10 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="29">
@@ -1635,7 +1624,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="32" t="s">
         <v>50</v>
@@ -1650,7 +1639,7 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>48</v>
@@ -1665,7 +1654,7 @@
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>49</v>
@@ -1680,10 +1669,10 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="28" t="s">
         <v>75</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>79</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="29">
@@ -1695,10 +1684,10 @@
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>51</v>
+        <v>73</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>76</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="27">
@@ -1710,10 +1699,10 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="27">
@@ -1725,10 +1714,10 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="27">
         <f t="shared" si="0"/>
@@ -1743,10 +1732,10 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="27">
         <f t="shared" si="0"/>
@@ -1761,10 +1750,10 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="27">
         <f t="shared" si="0"/>
@@ -1779,10 +1768,10 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="27">
         <f t="shared" si="0"/>
@@ -1797,10 +1786,10 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="27"/>
       <c r="E22" s="27">
@@ -1815,7 +1804,7 @@
         <v>29</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" s="27">
         <f t="shared" si="0"/>
@@ -1833,7 +1822,7 @@
         <v>29</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="27">
         <f t="shared" si="0"/>
@@ -1850,8 +1839,8 @@
       <c r="B25" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="30" t="s">
-        <v>77</v>
+      <c r="C25" s="35" t="s">
+        <v>78</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="31">
@@ -1866,7 +1855,7 @@
         <v>29</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="27">
         <f t="shared" si="0"/>
@@ -1884,7 +1873,7 @@
         <v>29</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="27">
         <f t="shared" si="0"/>
@@ -1902,7 +1891,7 @@
         <v>29</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D28" s="27">
         <f t="shared" si="0"/>
@@ -1920,7 +1909,7 @@
         <v>29</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" s="27">
         <f t="shared" si="0"/>
@@ -1938,7 +1927,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D30" s="27"/>
       <c r="E30" s="34">
@@ -1953,7 +1942,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="34">
